--- a/web/files/九龙-红磡-首岸第3期.xlsx
+++ b/web/files/九龙-红磡-首岸第3期.xlsx
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7011,14 +7011,14 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>8078400</v>
+        <v>7657600</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>23830</v>
+        <v>22589</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>8078400</v>
+        <v>7657600</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>23830</v>
+        <v>22589</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7874,34 +7874,34 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>11105000</v>
+        <v>10105500</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>25470</v>
+        <v>23178</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>10105550</v>
+        <v>10105500</v>
       </c>
       <c r="L117" s="5" t="n">
         <v>23178</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15257,7 +15257,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17241,7 +17241,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17551,7 +17551,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18890,7 +18890,7 @@
           <t>E | 391呎 (2房)
 $934万
 $23,876/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -18906,7 +18906,7 @@
           <t>G | 340呎 (2房)
 $803万
 $23,630/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -18993,7 +18993,7 @@
           <t>E | 391呎 (2房)
 $977万
 $24,999/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -19009,7 +19009,7 @@
           <t>G | 340呎 (2房)
 $798万
 $23,481/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -19017,7 +19017,7 @@
           <t>H | 339呎 (2房)
 $792万
 $23,359/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -19025,7 +19025,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,354/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -19033,7 +19033,7 @@
           <t>K | 339呎 (2房)
 $782万
 $23,080/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -19041,7 +19041,7 @@
           <t>L | 338呎 (2房)
 $778万
 $23,027/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -19096,7 +19096,7 @@
           <t>E | 391呎 (2房)
 $917万
 $23,464/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -19112,7 +19112,7 @@
           <t>G | 340呎 (2房)
 $794万
 $23,363/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -19120,7 +19120,7 @@
           <t>H | 339呎 (2房)
 $789万
 $23,263/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -19128,7 +19128,7 @@
           <t>J | 339呎 (2房)
 $788万
 $23,241/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -19136,7 +19136,7 @@
           <t>K | 339呎 (2房)
 $778万
 $22,965/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -19144,7 +19144,7 @@
           <t>L | 338呎 (2房)
 $774万
 $22,912/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -19152,7 +19152,7 @@
           <t>M | 616呎 (3房)
 $1443万
 $23,428/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -19167,7 +19167,7 @@
           <t>A | 708呎 (3房)
 $1668万
 $23,562/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -19199,7 +19199,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,287/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -19215,7 +19215,7 @@
           <t>G | 340呎 (2房)
 $791万
 $23,253/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -19223,7 +19223,7 @@
           <t>H | 339呎 (2房)
 $786万
 $23,174/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -19231,7 +19231,7 @@
           <t>J | 339呎 (2房)
 $784万
 $23,131/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
@@ -19239,7 +19239,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,887/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -19247,7 +19247,7 @@
           <t>L | 338呎 (2房)
 $770万
 $22,790/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -19270,7 +19270,7 @@
           <t>A | 708呎 (3房)
 $1661万
 $23,462/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -19286,7 +19286,7 @@
           <t>C | 431呎 (2房)
 $1030万
 $23,893/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -19294,7 +19294,7 @@
           <t>D | 436呎 (2房)
 $1013万
 $23,240/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -19302,7 +19302,7 @@
           <t>E | 391呎 (2房)
 $952万
 $24,356/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -19318,7 +19318,7 @@
           <t>G | 340呎 (2房)
 $804万
 $23,649/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -19326,7 +19326,7 @@
           <t>H | 339呎 (2房)
 $783万
 $23,099/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J9" s="22" t="inlineStr">
@@ -19334,7 +19334,7 @@
           <t>J | 339呎 (2房)
 $781万
 $23,050/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -19342,7 +19342,7 @@
           <t>K | 339呎 (2房)
 $773万
 $22,812/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
@@ -19350,7 +19350,7 @@
           <t>L | 338呎 (2房)
 $809万
 $23,946/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -19358,7 +19358,7 @@
           <t>M | 616呎 (3房)
 $1431万
 $23,223/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
           <t>A | 708呎 (3房)
 $1651万
 $23,324/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -19389,7 +19389,7 @@
           <t>C | 431呎 (2房)
 $1004万
 $23,301/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -19397,7 +19397,7 @@
           <t>D | 436呎 (2房)
 $1065万
 $24,434/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -19405,7 +19405,7 @@
           <t>E | 391呎 (2房)
 $897万
 $22,931/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -19421,7 +19421,7 @@
           <t>G | 340呎 (2房)
 $799万
 $23,510/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -19429,7 +19429,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,488/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -19437,7 +19437,7 @@
           <t>J | 339呎 (2房)
 $778万
 $22,935/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -19445,7 +19445,7 @@
           <t>K | 339呎 (2房)
 $770万
 $22,704/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -19453,7 +19453,7 @@
           <t>L | 338呎 (2房)
 $764万
 $22,591/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -19476,7 +19476,7 @@
           <t>A | 708呎 (3房)
 $1642万
 $23,187/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -19492,7 +19492,7 @@
           <t>C | 431呎 (2房)
 $1023万
 $23,731/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -19500,7 +19500,7 @@
           <t>D | 436呎 (2房)
 $1006万
 $23,082/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -19508,7 +19508,7 @@
           <t>E | 391呎 (2房)
 $911万
 $23,295/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -19524,7 +19524,7 @@
           <t>G | 340呎 (2房)
 $777万
 $22,865/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -19532,7 +19532,7 @@
           <t>H | 339呎 (2房)
 $776万
 $22,884/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -19540,7 +19540,7 @@
           <t>J | 339呎 (2房)
 $774万
 $22,836/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -19548,7 +19548,7 @@
           <t>K | 339呎 (2房)
 $767万
 $22,613/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -19556,7 +19556,7 @@
           <t>L | 338呎 (2房)
 $759万
 $22,457/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
@@ -19564,7 +19564,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $23,008/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
           <t>A | 708呎 (3房)
 $1632万
 $23,048/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -19603,7 +19603,7 @@
           <t>D | 436呎 (2房)
 $1001万
 $22,965/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -19611,7 +19611,7 @@
           <t>E | 391呎 (2房)
 $904万
 $23,114/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -19619,7 +19619,7 @@
           <t>F | 436呎 (2房)
 $1018万
 $23,355/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -19627,7 +19627,7 @@
           <t>G | 340呎 (2房)
 $773万
 $22,747/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -19635,7 +19635,7 @@
           <t>H | 339呎 (2房)
 $771万
 $22,745/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -19643,7 +19643,7 @@
           <t>J | 339呎 (2房)
 $771万
 $22,739/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -19651,7 +19651,7 @@
           <t>K | 339呎 (2房)
 $779万
 $22,973/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
@@ -19659,7 +19659,7 @@
           <t>L | 338呎 (2房)
 $756万
 $22,362/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -19667,7 +19667,7 @@
           <t>M | 616呎 (3房)
 $1414万
 $22,949/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19682,7 @@
           <t>A | 708呎 (3房)
 $1624万
 $22,931/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -19690,7 +19690,7 @@
           <t>B | 610呎 (3房)
 $1443万
 $23,655/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -19706,7 +19706,7 @@
           <t>D | 436呎 (2房)
 $1048万
 $24,044/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -19714,7 +19714,7 @@
           <t>E | 391呎 (2房)
 $880万
 $22,501/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -19722,7 +19722,7 @@
           <t>F | 436呎 (2房)
 $1015万
 $23,282/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -19730,15 +19730,15 @@
           <t>G | 340呎 (2房)
 $769万
 $22,629/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
           <t>H | 339呎 (2房)
-$808万
-$23,830/呎
-(26年-06月-07日)</t>
+$766万
+$22,589/呎
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J13" s="22" t="inlineStr">
@@ -19746,7 +19746,7 @@
           <t>J | 339呎 (2房)
 $765万
 $22,576/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -19754,7 +19754,7 @@
           <t>K | 339呎 (2房)
 $757万
 $22,328/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L13" s="22" t="inlineStr">
@@ -19762,7 +19762,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,209/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -19770,7 +19770,7 @@
           <t>M | 616呎 (3房)
 $1406万
 $22,831/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
           <t>A | 708呎 (3房)
 $1612万
 $22,774/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -19793,7 +19793,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,011/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -19801,7 +19801,7 @@
           <t>C | 431呎 (2房)
 $990万
 $22,963/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -19809,7 +19809,7 @@
           <t>D | 436呎 (2房)
 $988万
 $22,656/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -19817,15 +19817,15 @@
           <t>E | 391呎 (2房)
 $874万
 $22,347/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 436呎 (2房)
-$1110万
-$25,470/呎
-(在售)</t>
+$1011万
+$23,178/呎
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -19833,7 +19833,7 @@
           <t>G | 340呎 (2房)
 $763万
 $22,456/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -19841,7 +19841,7 @@
           <t>H | 339呎 (2房)
 $802万
 $23,660/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -19849,7 +19849,7 @@
           <t>J | 339呎 (2房)
 $802万
 $23,652/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -19857,7 +19857,7 @@
           <t>K | 339呎 (2房)
 $793万
 $23,394/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
@@ -19865,7 +19865,7 @@
           <t>L | 338呎 (2房)
 $746万
 $22,058/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
@@ -19873,7 +19873,7 @@
           <t>M | 616呎 (3房)
 $1394万
 $22,638/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
           <t>A | 708呎 (3房)
 $1688万
 $23,848/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -19896,7 +19896,7 @@
           <t>B | 610呎 (3房)
 $1471万
 $24,109/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -19912,7 +19912,7 @@
           <t>D | 436呎 (2房)
 $980万
 $22,487/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -19920,7 +19920,7 @@
           <t>E | 391呎 (2房)
 $869万
 $22,231/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -19928,7 +19928,7 @@
           <t>F | 436呎 (2房)
 $1006万
 $23,067/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -19936,7 +19936,7 @@
           <t>G | 340呎 (2房)
 $759万
 $22,338/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -19944,7 +19944,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,493/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -19952,7 +19952,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,264/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -19960,7 +19960,7 @@
           <t>K | 339呎 (2房)
 $748万
 $22,063/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -19968,7 +19968,7 @@
           <t>L | 338呎 (2房)
 $758万
 $22,425/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -19976,7 +19976,7 @@
           <t>M | 616呎 (3房)
 $1413万
 $22,936/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -19991,7 +19991,7 @@
           <t>A | 708呎 (3房)
 $1673万
 $23,631/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -19999,7 +19999,7 @@
           <t>B | 610呎 (3房)
 $1386万
 $22,722/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -20007,7 +20007,7 @@
           <t>C | 431呎 (2房)
 $1035万
 $24,004/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -20015,7 +20015,7 @@
           <t>D | 436呎 (2房)
 $973万
 $22,324/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -20023,7 +20023,7 @@
           <t>E | 391呎 (2房)
 $863万
 $22,080/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -20031,7 +20031,7 @@
           <t>F | 436呎 (2房)
 $998万
 $22,881/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -20039,7 +20039,7 @@
           <t>G | 340呎 (2房)
 $772万
 $22,692/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -20047,7 +20047,7 @@
           <t>H | 339呎 (2房)
 $751万
 $22,159/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -20055,7 +20055,7 @@
           <t>J | 339呎 (2房)
 $792万
 $23,365/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -20063,7 +20063,7 @@
           <t>K | 339呎 (2房)
 $760万
 $22,432/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -20071,7 +20071,7 @@
           <t>L | 338呎 (2房)
 $738万
 $21,835/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -20079,7 +20079,7 @@
           <t>M | 616呎 (3房)
 $1372万
 $22,273/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
           <t>A | 708呎 (3房)
 $1577万
 $22,281/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -20102,7 +20102,7 @@
           <t>B | 610呎 (3房)
 $1379万
 $22,602/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -20110,7 +20110,7 @@
           <t>C | 431呎 (2房)
 $976万
 $22,653/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -20118,7 +20118,7 @@
           <t>D | 436呎 (2房)
 $987万
 $22,629/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -20126,7 +20126,7 @@
           <t>E | 391呎 (2房)
 $855万
 $21,875/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -20134,7 +20134,7 @@
           <t>F | 436呎 (2房)
 $987万
 $22,633/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -20142,7 +20142,7 @@
           <t>G | 340呎 (2房)
 $751万
 $22,078/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -20150,7 +20150,7 @@
           <t>H | 339呎 (2房)
 $746万
 $22,009/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -20158,7 +20158,7 @@
           <t>J | 339呎 (2房)
 $746万
 $22,012/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -20166,7 +20166,7 @@
           <t>K | 339呎 (2房)
 $758万
 $22,350/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -20174,7 +20174,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,746/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -20182,7 +20182,7 @@
           <t>M | 616呎 (3房)
 $1387万
 $22,518/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20197,7 +20197,7 @@
           <t>A | 708呎 (3房)
 $1569万
 $22,166/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -20205,7 +20205,7 @@
           <t>B | 610呎 (3房)
 $1404万
 $23,015/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -20213,7 +20213,7 @@
           <t>C | 431呎 (2房)
 $970万
 $22,497/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -20221,7 +20221,7 @@
           <t>D | 436呎 (2房)
 $960万
 $22,013/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -20229,7 +20229,7 @@
           <t>E | 391呎 (2房)
 $895万
 $22,897/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -20237,7 +20237,7 @@
           <t>F | 436呎 (2房)
 $1000万
 $22,947/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -20245,7 +20245,7 @@
           <t>G | 340呎 (2房)
 $745万
 $21,912/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -20253,7 +20253,7 @@
           <t>H | 339呎 (2房)
 $741万
 $21,867/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -20261,7 +20261,7 @@
           <t>J | 339呎 (2房)
 $744万
 $21,945/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -20269,7 +20269,7 @@
           <t>K | 339呎 (2房)
 $737万
 $21,730/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -20277,7 +20277,7 @@
           <t>L | 338呎 (2房)
 $730万
 $21,611/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -20285,7 +20285,7 @@
           <t>M | 616呎 (3房)
 $1417万
 $22,998/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20300,7 @@
           <t>A | 708呎 (3房)
 $1561万
 $22,049/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -20308,7 +20308,7 @@
           <t>B | 610呎 (3房)
 $1367万
 $22,404/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -20316,7 +20316,7 @@
           <t>C | 431呎 (2房)
 $965万
 $22,381/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -20324,7 +20324,7 @@
           <t>D | 436呎 (2房)
 $955万
 $21,898/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -20332,7 +20332,7 @@
           <t>E | 391呎 (2房)
 $842万
 $21,533/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -20340,7 +20340,7 @@
           <t>F | 436呎 (2房)
 $971万
 $22,280/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -20348,7 +20348,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,295/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -20356,7 +20356,7 @@
           <t>H | 339呎 (2房)
 $738万
 $21,783/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>J | 339呎 (2房)
 $782万
 $23,063/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>K | 339呎 (2房)
 $750万
 $22,128/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>L | 338呎 (2房)
 $744万
 $22,004/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>M | 616呎 (3房)
 $1407万
 $22,836/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
           <t>A | 708呎 (3房)
 $1553万
 $21,935/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -20411,7 +20411,7 @@
           <t>B | 610呎 (3房)
 $1361万
 $22,305/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -20419,7 +20419,7 @@
           <t>C | 431呎 (2房)
 $979万
 $22,719/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -20427,7 +20427,7 @@
           <t>D | 436呎 (2房)
 $952万
 $21,829/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -20435,7 +20435,7 @@
           <t>E | 391呎 (2房)
 $835万
 $21,365/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -20443,7 +20443,7 @@
           <t>F | 436呎 (2房)
 $1017万
 $23,322/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -20451,7 +20451,7 @@
           <t>G | 340呎 (2房)
 $738万
 $21,719/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -20459,7 +20459,7 @@
           <t>H | 339呎 (2房)
 $736万
 $21,703/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -20467,7 +20467,7 @@
           <t>J | 339呎 (2房)
 $755万
 $22,262/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -20475,7 +20475,7 @@
           <t>K | 339呎 (2房)
 $731万
 $21,577/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -20483,7 +20483,7 @@
           <t>L | 338呎 (2房)
 $725万
 $21,455/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -20491,7 +20491,7 @@
           <t>M | 616呎 (3房)
 $1324万
 $21,497/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20506,7 @@
           <t>A | 708呎 (3房)
 $1580万
 $22,323/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -20514,7 +20514,7 @@
           <t>B | 610呎 (3房)
 $1355万
 $22,210/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -20522,7 +20522,7 @@
           <t>C | 431呎 (2房)
 $972万
 $22,549/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -20530,7 +20530,7 @@
           <t>D | 436呎 (2房)
 $969万
 $22,235/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -20538,7 +20538,7 @@
           <t>E | 391呎 (2房)
 $876万
 $22,397/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -20546,7 +20546,7 @@
           <t>F | 436呎 (2房)
 $978万
 $22,427/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -20554,7 +20554,7 @@
           <t>G | 340呎 (2房)
 $735万
 $21,623/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -20562,7 +20562,7 @@
           <t>H | 339呎 (2房)
 $750万
 $22,117/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -20570,7 +20570,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -20578,7 +20578,7 @@
           <t>K | 339呎 (2房)
 $728万
 $21,480/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -20586,7 +20586,7 @@
           <t>L | 338呎 (2房)
 $722万
 $21,358/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -20594,7 +20594,7 @@
           <t>M | 616呎 (3房)
 $1315万
 $21,348/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
           <t>A | 708呎 (3房)
 $1539万
 $21,731/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -20617,7 +20617,7 @@
           <t>B | 610呎 (3房)
 $1349万
 $22,117/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -20625,7 +20625,7 @@
           <t>C | 431呎 (2房)
 $945万
 $21,931/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -20633,7 +20633,7 @@
           <t>D | 436呎 (2房)
 $944万
 $21,662/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -20641,7 +20641,7 @@
           <t>E | 391呎 (2房)
 $871万
 $22,279/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -20649,7 +20649,7 @@
           <t>F | 436呎 (2房)
 $948万
 $21,742/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -20657,7 +20657,7 @@
           <t>G | 340呎 (2房)
 $731万
 $21,505/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -20665,7 +20665,7 @@
           <t>H | 339呎 (2房)
 $732万
 $21,601/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -20673,7 +20673,7 @@
           <t>J | 339呎 (2房)
 $772万
 $22,771/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -20681,7 +20681,7 @@
           <t>K | 339呎 (2房)
 $725万
 $21,383/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -20689,7 +20689,7 @@
           <t>L | 338呎 (2房)
 $735万
 $21,731/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -20697,7 +20697,7 @@
           <t>M | 616呎 (3房)
 $1307万
 $21,215/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
           <t>A | 708呎 (3房)
 $1618万
 $22,846/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -20728,7 +20728,7 @@
           <t>C | 431呎 (2房)
 $940万
 $21,802/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -20736,7 +20736,7 @@
           <t>D | 436呎 (2房)
 $990万
 $22,716/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -20744,7 +20744,7 @@
           <t>E | 391呎 (2房)
 $822万
 $21,028/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -20752,7 +20752,7 @@
           <t>F | 436呎 (2房)
 $938万
 $21,516/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -20760,7 +20760,7 @@
           <t>G | 340呎 (2房)
 $743万
 $21,860/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -20768,7 +20768,7 @@
           <t>H | 339呎 (2房)
 $768万
 $22,643/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -20776,7 +20776,7 @@
           <t>J | 339呎 (2房)
 $767万
 $22,632/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -20784,7 +20784,7 @@
           <t>K | 339呎 (2房)
 $736万
 $21,722/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -20792,7 +20792,7 @@
           <t>L | 338呎 (2房)
 $731万
 $21,632/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -20800,7 +20800,7 @@
           <t>M | 616呎 (3房)
 $1328万
 $21,567/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -20815,7 +20815,7 @@
           <t>A | 708呎 (3房)
 $1528万
 $21,575/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -20831,7 +20831,7 @@
           <t>C | 431呎 (2房)
 $934万
 $21,665/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -20839,7 +20839,7 @@
           <t>D | 436呎 (2房)
 $933万
 $21,400/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -20847,7 +20847,7 @@
           <t>E | 391呎 (2房)
 $819万
 $20,944/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -20855,7 +20855,7 @@
           <t>F | 436呎 (2房)
 $931万
 $21,343/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -20863,7 +20863,7 @@
           <t>G | 340呎 (2房)
 $724万
 $21,291/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -20871,7 +20871,7 @@
           <t>H | 339呎 (2房)
 $764万
 $22,544/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -20879,7 +20879,7 @@
           <t>J | 339呎 (2房)
 $764万
 $22,524/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -20887,7 +20887,7 @@
           <t>K | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -20895,7 +20895,7 @@
           <t>L | 338呎 (2房)
 $751万
 $22,208/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -20903,7 +20903,7 @@
           <t>M | 616呎 (3房)
 $1293万
 $20,989/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20918,7 @@
           <t>A | 708呎 (3房)
 $1604万
 $22,649/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -20926,7 +20926,7 @@
           <t>B | 610呎 (3房)
 $1399万
 $22,938/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -20934,7 +20934,7 @@
           <t>C | 431呎 (2房)
 $928万
 $21,542/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -20942,7 +20942,7 @@
           <t>D | 436呎 (2房)
 $928万
 $21,295/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -20950,7 +20950,7 @@
           <t>E | 391呎 (2房)
 $815万
 $20,837/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -20958,7 +20958,7 @@
           <t>F | 436呎 (2房)
 $923万
 $21,176/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -20966,7 +20966,7 @@
           <t>G | 340呎 (2房)
 $758万
 $22,300/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -20974,7 +20974,7 @@
           <t>H | 339呎 (2房)
 $720万
 $21,233/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -20982,7 +20982,7 @@
           <t>J | 339呎 (2房)
 $758万
 $22,363/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -20990,7 +20990,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,013/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -20998,7 +20998,7 @@
           <t>L | 338呎 (2房)
 $723万
 $21,404/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -21006,7 +21006,7 @@
           <t>M | 616呎 (3房)
 $1284万
 $20,841/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21021,7 @@
           <t>A | 708呎 (3房)
 $1548万
 $21,865/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -21029,7 +21029,7 @@
           <t>B | 610呎 (3房)
 $1347万
 $22,087/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -21037,7 +21037,7 @@
           <t>C | 431呎 (2房)
 $923万
 $21,411/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -21045,7 +21045,7 @@
           <t>D | 436呎 (2房)
 $922万
 $21,147/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -21053,7 +21053,7 @@
           <t>E | 391呎 (2房)
 $808万
 $20,672/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -21061,7 +21061,7 @@
           <t>F | 436呎 (2房)
 $916万
 $21,007/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -21069,7 +21069,7 @@
           <t>G | 340呎 (2房)
 $752万
 $22,125/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -21077,7 +21077,7 @@
           <t>H | 339呎 (2房)
 $713万
 $21,045/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -21085,7 +21085,7 @@
           <t>J | 339呎 (2房)
 $752万
 $22,182/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -21093,7 +21093,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,046/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -21101,7 +21101,7 @@
           <t>L | 338呎 (2房)
 $703万
 $20,812/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -21109,7 +21109,7 @@
           <t>M | 616呎 (3房)
 $1275万
 $20,695/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21124,7 @@
           <t>A | 708呎 (3房)
 $1541万
 $21,771/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -21132,7 +21132,7 @@
           <t>B | 610呎 (3房)
 $1309万
 $21,464/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -21140,7 +21140,7 @@
           <t>C | 431呎 (2房)
 $917万
 $21,283/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -21148,7 +21148,7 @@
           <t>D | 436呎 (2房)
 $917万
 $21,022/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -21156,7 +21156,7 @@
           <t>E | 391呎 (2房)
 $802万
 $20,504/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -21164,7 +21164,7 @@
           <t>F | 436呎 (2房)
 $958万
 $21,983/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -21172,7 +21172,7 @@
           <t>G | 340呎 (2房)
 $707万
 $20,804/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -21180,7 +21180,7 @@
           <t>H | 339呎 (2房)
 $708万
 $20,892/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -21188,7 +21188,7 @@
           <t>J | 339呎 (2房)
 $708万
 $20,876/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -21196,7 +21196,7 @@
           <t>K | 339呎 (2房)
 $718万
 $21,190/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -21204,7 +21204,7 @@
           <t>L | 338呎 (2房)
 $699万
 $20,666/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -21212,7 +21212,7 @@
           <t>M | 616呎 (3房)
 $1267万
 $20,564/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
           <t>E | 391呎 (2房)
 $796万
 $20,357/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -21275,7 +21275,7 @@
           <t>G | 302呎 (2房)
 $727万
 $24,085/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -21283,7 +21283,7 @@
           <t>H | 301呎 (2房)
 $724万
 $24,056/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -21291,7 +21291,7 @@
           <t>J | 301呎 (2房)
 $723万
 $24,032/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -21299,7 +21299,7 @@
           <t>K | 301呎 (2房)
 $757万
 $25,142/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -21307,7 +21307,7 @@
           <t>L | 301呎 (2房)
 $714万
 $23,705/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -21315,7 +21315,7 @@
           <t>M | 616呎 (3房)
 $1256万
 $20,383/呎
-(26年-05月-09日)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-红磡-首岸第3期.xlsx
+++ b/web/files/九龙-红磡-首岸第3期.xlsx
@@ -2291,14 +2291,14 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>14431600</v>
+        <v>14748800</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>23428</v>
+        <v>23943</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>14431600</v>
+        <v>14748800</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>23428</v>
+        <v>23943</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -19150,9 +19150,9 @@
       <c r="M7" s="22" t="inlineStr">
         <is>
           <t>M | 616呎 (3房)
-$1443万
-$23,428/呎
-(26年-06月-04日)</t>
+$1475万
+$23,943/呎
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-红磡-首岸第3期.xlsx
+++ b/web/files/九龙-红磡-首岸第3期.xlsx
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -19825,7 +19825,7 @@
           <t>F | 436呎 (2房)
 $1011万
 $23,178/呎
-(26年-07月-23日)</t>
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
